--- a/docs/downloads/04/tbl_raisons_non_scol_alaotra_analamiranga.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_alaotra_analamiranga.xlsx
@@ -405,12 +405,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Famine</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>8.300000000000001</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>8.300000000000001</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +441,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +453,6 @@
           <t>Sans intérêt (famille)</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -512,12 +482,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>4.2</v>
       </c>
     </row>
   </sheetData>
